--- a/data/trans_bre/IP16B98-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP16B98-Estudios-trans_bre.xlsx
@@ -661,22 +661,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-18,33; 9,73</t>
+          <t>-19,09; 9,65</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,39</t>
+          <t>0,0; 20,89</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-19,45; 10,73</t>
+          <t>-20,24; 10,63</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,56</t>
+          <t>0,0; 26,41</t>
         </is>
       </c>
     </row>
@@ -721,22 +721,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-44,8; 55,42</t>
+          <t>-44,65; 55,49</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-30,07; 51,99</t>
+          <t>-30,07; 52,37</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-45,62; 124,57</t>
+          <t>-45,13; 124,75</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-33,34; 108,3</t>
+          <t>-32,84; 109,58</t>
         </is>
       </c>
     </row>
@@ -781,22 +781,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-13,86; 16,2</t>
+          <t>-11,01; 16,41</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,76; 17,21</t>
+          <t>-3,73; 16,81</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-14,33; 19,87</t>
+          <t>-11,43; 20,33</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,93; 21,45</t>
+          <t>-4,01; 20,64</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP16B98-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP16B98-Estudios-trans_bre.xlsx
@@ -661,22 +661,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-19,09; 9,65</t>
+          <t>-18,4; 9,66</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,89</t>
+          <t>0,0; 20,79</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-20,24; 10,63</t>
+          <t>-19,48; 10,67</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,41</t>
+          <t>0,0; 26,25</t>
         </is>
       </c>
     </row>
@@ -721,22 +721,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-44,65; 55,49</t>
+          <t>-45,13; 55,42</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-30,07; 52,37</t>
+          <t>-29,7; 53,86</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-45,13; 124,75</t>
+          <t>-45,62; 124,64</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-32,84; 109,58</t>
+          <t>-30,5; 116,94</t>
         </is>
       </c>
     </row>
@@ -781,22 +781,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-11,01; 16,41</t>
+          <t>-12,83; 14,65</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,73; 16,81</t>
+          <t>-4,58; 16,76</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-11,43; 20,33</t>
+          <t>-13,96; 17,84</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,01; 20,64</t>
+          <t>-4,7; 20,41</t>
         </is>
       </c>
     </row>
